--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221001</v>
+        <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>79917</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,22 +1058,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjeforsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516801</v>
+        <v>516166</v>
       </c>
       <c r="R5" t="n">
-        <v>6878329</v>
+        <v>6878574</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,12 +1094,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1116,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,6 +1139,121 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137007706</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125221001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öjeforsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516801</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6878329</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125221001</t>
         </is>
@@ -1144,6 +1265,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23643-2025 artfynd.xlsx
+++ b/artfynd/A 23643-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137007706</v>
       </c>
       <c r="B5" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
